--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:5443da66-91e5-42ea-aeb4-b00b98188e47</t>
+    <t>urn:uuid:5b4c92c6-8415-4e2f-81b2-68fbd92f5898</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:5b4c92c6-8415-4e2f-81b2-68fbd92f5898</t>
+    <t>urn:uuid:244927b3-1cf6-4a3b-962a-73844a510754</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:244927b3-1cf6-4a3b-962a-73844a510754</t>
+    <t>urn:uuid:84f03d43-23c7-4cca-8453-4a2bd7932753</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Expansion" r:id="rId4" sheetId="2"/>
+    <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:84f03d43-23c7-4cca-8453-4a2bd7932753</t>
+    <t>urn:uuid:b273821e-88ee-400b-b05c-40c3b1f7d7cf</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,9 +37,15 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Conditions</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
+    <t>Antimicrobiology - Vaginitis-related conditions</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -48,6 +55,9 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -57,6 +67,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Antimicrobiology - S2 Get data to collect - Response - 1.4. ValueSet</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -69,6 +82,9 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
+    <t>ValueSet URL</t>
+  </si>
+  <si>
     <t>Level</t>
   </si>
   <si>
@@ -93,13 +109,13 @@
     <t>1</t>
   </si>
   <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>419760006</t>
   </si>
   <si>
     <t>Bacterial vaginosis</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>276877003</t>
@@ -280,64 +296,72 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>17</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -346,88 +370,113 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>31</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:b273821e-88ee-400b-b05c-40c3b1f7d7cf</t>
+    <t>urn:uuid:5dabd7ea-0d0e-442c-83b5-3b690a65a014</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:5dabd7ea-0d0e-442c-83b5-3b690a65a014</t>
+    <t>urn:uuid:9d37c634-a224-4647-86ed-8402b5a23610</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:9d37c634-a224-4647-86ed-8402b5a23610</t>
+    <t>urn:uuid:9564b7d6-8994-4790-87db-b7412cb96491</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:9564b7d6-8994-4790-87db-b7412cb96491</t>
+    <t>urn:uuid:f0ad5cab-bd0d-45f7-b8a5-08cfedbc3fe8</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:f0ad5cab-bd0d-45f7-b8a5-08cfedbc3fe8</t>
+    <t>urn:uuid:0b7539cc-1ae0-4b40-9f8f-601544d75e7f</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:0b7539cc-1ae0-4b40-9f8f-601544d75e7f</t>
+    <t>urn:uuid:08f6305d-5d37-4853-9301-993cd258b698</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:08f6305d-5d37-4853-9301-993cd258b698</t>
+    <t>urn:uuid:b43447cf-1449-4799-81a1-51c876f9c9bf</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:b43447cf-1449-4799-81a1-51c876f9c9bf</t>
+    <t>urn:uuid:3eb38227-bd54-4c01-9327-b7f3bb6d068f</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:3eb38227-bd54-4c01-9327-b7f3bb6d068f</t>
+    <t>urn:uuid:f7b71489-ef57-4ce4-aa76-132b499688c8</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -7,14 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>Property</t>
   </si>
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:f7b71489-ef57-4ce4-aa76-132b499688c8</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/medication/ValueSet/PregnancyCodes</t>
   </si>
   <si>
     <t>Version</t>
@@ -37,13 +37,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Conditions</t>
+    <t>PregnancyCodes</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Antimicrobiology - Vaginitis-related conditions</t>
+    <t>Pregnancy Codes</t>
   </si>
   <si>
     <t>Status</t>
@@ -55,9 +55,6 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -67,9 +64,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Antimicrobiology - S2 Get data to collect - Response - 1.4. ValueSet</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -82,52 +76,31 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>ValueSet URL</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>Inactive</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>Z33.1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/sid/icd-10</t>
+  </si>
+  <si>
+    <t>87527008</t>
+  </si>
+  <si>
+    <t>127364007</t>
+  </si>
+  <si>
+    <t>72892002</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>419760006</t>
-  </si>
-  <si>
-    <t>Bacterial vaginosis</t>
-  </si>
-  <si>
-    <t>276877003</t>
-  </si>
-  <si>
-    <t>Trichomonal vaginitis</t>
-  </si>
-  <si>
-    <t>72934000</t>
-  </si>
-  <si>
-    <t>Candidiasis of vagina</t>
   </si>
 </sst>
 </file>
@@ -320,48 +293,46 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
-      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -371,7 +342,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -380,7 +351,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
         <v>22</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -390,93 +386,53 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="F1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -7,14 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/ValueSet/PregnancyCodes</t>
+    <t>urn:uuid:d50050df-b0fe-4a44-8902-da7bfcf6b370</t>
   </si>
   <si>
     <t>Version</t>
@@ -37,13 +37,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>PregnancyCodes</t>
+    <t>Conditions</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Pregnancy Codes</t>
+    <t>Antimicrobiology - Vaginitis-related conditions</t>
   </si>
   <si>
     <t>Status</t>
@@ -55,6 +55,9 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Antimicrobiology - S2 Get data to collect - Response - 1.4. ValueSet</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -76,31 +82,52 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>Z33.1</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/sid/icd-10</t>
-  </si>
-  <si>
-    <t>87527008</t>
-  </si>
-  <si>
-    <t>127364007</t>
-  </si>
-  <si>
-    <t>72892002</t>
+    <t>ValueSet URL</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>419760006</t>
+  </si>
+  <si>
+    <t>Bacterial vaginosis</t>
+  </si>
+  <si>
+    <t>276877003</t>
+  </si>
+  <si>
+    <t>Trichomonal vaginitis</t>
+  </si>
+  <si>
+    <t>72934000</t>
+  </si>
+  <si>
+    <t>Candidiasis of vagina</t>
   </si>
 </sst>
 </file>
@@ -293,46 +320,48 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -342,7 +371,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -351,32 +380,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>20</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -386,53 +390,93 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>24</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:d50050df-b0fe-4a44-8902-da7bfcf6b370</t>
+    <t>urn:uuid:4def8174-ee4e-4fda-a69a-9e1ea685058e</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:4def8174-ee4e-4fda-a69a-9e1ea685058e</t>
+    <t>urn:uuid:bf426a35-6655-42a0-a195-1effcab5f717</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -7,14 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>Property</t>
   </si>
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:bf426a35-6655-42a0-a195-1effcab5f717</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/medication/ValueSet/PregnancyCodes</t>
   </si>
   <si>
     <t>Version</t>
@@ -37,13 +37,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Conditions</t>
+    <t>PregnancyCodes</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Antimicrobiology - Vaginitis-related conditions</t>
+    <t>Pregnancy Codes</t>
   </si>
   <si>
     <t>Status</t>
@@ -55,9 +55,6 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -67,9 +64,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Antimicrobiology - S2 Get data to collect - Response - 1.4. ValueSet</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -82,52 +76,31 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>ValueSet URL</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>Inactive</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>Z33.1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/sid/icd-10</t>
+  </si>
+  <si>
+    <t>87527008</t>
+  </si>
+  <si>
+    <t>127364007</t>
+  </si>
+  <si>
+    <t>72892002</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>419760006</t>
-  </si>
-  <si>
-    <t>Bacterial vaginosis</t>
-  </si>
-  <si>
-    <t>276877003</t>
-  </si>
-  <si>
-    <t>Trichomonal vaginitis</t>
-  </si>
-  <si>
-    <t>72934000</t>
-  </si>
-  <si>
-    <t>Candidiasis of vagina</t>
   </si>
 </sst>
 </file>
@@ -320,48 +293,46 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
-      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -371,7 +342,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -380,7 +351,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
         <v>22</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -390,93 +386,53 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="F1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -7,14 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/ValueSet/PregnancyCodes</t>
+    <t>urn:uuid:2f89f266-7a71-4f79-97bc-e44635d7df67</t>
   </si>
   <si>
     <t>Version</t>
@@ -37,13 +37,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>PregnancyCodes</t>
+    <t>Conditions</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Pregnancy Codes</t>
+    <t>Antimicrobiology - Vaginitis-related conditions</t>
   </si>
   <si>
     <t>Status</t>
@@ -55,6 +55,9 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Antimicrobiology - S2 Get data to collect - Response - 1.4. ValueSet</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -76,31 +82,52 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>Z33.1</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/sid/icd-10</t>
-  </si>
-  <si>
-    <t>87527008</t>
-  </si>
-  <si>
-    <t>127364007</t>
-  </si>
-  <si>
-    <t>72892002</t>
+    <t>ValueSet URL</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>419760006</t>
+  </si>
+  <si>
+    <t>Bacterial vaginosis</t>
+  </si>
+  <si>
+    <t>276877003</t>
+  </si>
+  <si>
+    <t>Trichomonal vaginitis</t>
+  </si>
+  <si>
+    <t>72934000</t>
+  </si>
+  <si>
+    <t>Candidiasis of vagina</t>
   </si>
 </sst>
 </file>
@@ -293,46 +320,48 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -342,7 +371,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -351,32 +380,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>20</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -386,53 +390,93 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>24</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -7,14 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>Property</t>
   </si>
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:2f89f266-7a71-4f79-97bc-e44635d7df67</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/medication/ValueSet/PregnancyCodes</t>
   </si>
   <si>
     <t>Version</t>
@@ -37,13 +37,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Conditions</t>
+    <t>PregnancyCodes</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Antimicrobiology - Vaginitis-related conditions</t>
+    <t>Pregnancy Codes</t>
   </si>
   <si>
     <t>Status</t>
@@ -55,9 +55,6 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -67,9 +64,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Antimicrobiology - S2 Get data to collect - Response - 1.4. ValueSet</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -82,52 +76,31 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>ValueSet URL</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>Inactive</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>Z33.1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/sid/icd-10</t>
+  </si>
+  <si>
+    <t>87527008</t>
+  </si>
+  <si>
+    <t>127364007</t>
+  </si>
+  <si>
+    <t>72892002</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>419760006</t>
-  </si>
-  <si>
-    <t>Bacterial vaginosis</t>
-  </si>
-  <si>
-    <t>276877003</t>
-  </si>
-  <si>
-    <t>Trichomonal vaginitis</t>
-  </si>
-  <si>
-    <t>72934000</t>
-  </si>
-  <si>
-    <t>Candidiasis of vagina</t>
   </si>
 </sst>
 </file>
@@ -320,48 +293,46 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
-      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -371,7 +342,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -380,7 +351,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
         <v>22</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -390,93 +386,53 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="F1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>13</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -7,14 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/ValueSet/PregnancyCodes</t>
+    <t>urn:uuid:aec927b2-287d-4d30-97d3-e89bbd93a95b</t>
   </si>
   <si>
     <t>Version</t>
@@ -37,13 +37,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>PregnancyCodes</t>
+    <t>Conditions</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Pregnancy Codes</t>
+    <t>Antimicrobiology - Vaginitis-related conditions</t>
   </si>
   <si>
     <t>Status</t>
@@ -55,6 +55,9 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Antimicrobiology - S2 Get data to collect - Response - 1.4. ValueSet</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -76,31 +82,52 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>Z33.1</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/sid/icd-10</t>
-  </si>
-  <si>
-    <t>87527008</t>
-  </si>
-  <si>
-    <t>127364007</t>
-  </si>
-  <si>
-    <t>72892002</t>
+    <t>ValueSet URL</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>419760006</t>
+  </si>
+  <si>
+    <t>Bacterial vaginosis</t>
+  </si>
+  <si>
+    <t>276877003</t>
+  </si>
+  <si>
+    <t>Trichomonal vaginitis</t>
+  </si>
+  <si>
+    <t>72934000</t>
+  </si>
+  <si>
+    <t>Candidiasis of vagina</t>
   </si>
 </sst>
 </file>
@@ -293,46 +320,48 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -342,7 +371,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -351,32 +380,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>20</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -386,53 +390,93 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>24</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:aec927b2-287d-4d30-97d3-e89bbd93a95b</t>
+    <t>urn:uuid:3f82e709-17e1-4ced-9c2c-f5a9cc7e6288</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:3f82e709-17e1-4ced-9c2c-f5a9cc7e6288</t>
+    <t>urn:uuid:301d535a-2818-4148-8276-1545e5dd8d77</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:301d535a-2818-4148-8276-1545e5dd8d77</t>
+    <t>urn:uuid:ad70f35e-c932-4f75-affa-a418490daecf</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:ad70f35e-c932-4f75-affa-a418490daecf</t>
+    <t>urn:uuid:06a690e4-cdd0-426d-a6af-fc0ddfa1424f</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:06a690e4-cdd0-426d-a6af-fc0ddfa1424f</t>
+    <t>urn:uuid:967a5991-0eaa-4e4f-b8b4-38caca83d396</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:967a5991-0eaa-4e4f-b8b4-38caca83d396</t>
+    <t>urn:uuid:867afd54-c338-4e54-82b2-3a8a789419fd</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:867afd54-c338-4e54-82b2-3a8a789419fd</t>
+    <t>urn:uuid:af3502db-f3ef-4eb8-b6dc-1257b145f2cf</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:af3502db-f3ef-4eb8-b6dc-1257b145f2cf</t>
+    <t>urn:uuid:c6c13927-2fa0-451b-a403-4a31c7a652ea</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:c6c13927-2fa0-451b-a403-4a31c7a652ea</t>
+    <t>urn:uuid:ede819df-e975-445e-a2d2-9aa6068a5e88</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:ede819df-e975-445e-a2d2-9aa6068a5e88</t>
+    <t>urn:uuid:956bfe92-0223-4e91-953f-6332d6c67736</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:956bfe92-0223-4e91-953f-6332d6c67736</t>
+    <t>urn:uuid:2e99e97e-dc25-4736-b324-b2ed19384b89</t>
   </si>
   <si>
     <t>Version</t>

--- a/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:2e99e97e-dc25-4736-b324-b2ed19384b89</t>
+    <t>urn:uuid:293ff821-ef38-43d0-9c74-58fef8124621</t>
   </si>
   <si>
     <t>Version</t>
